--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="208">
   <si>
     <t>targa</t>
   </si>
@@ -470,178 +470,175 @@
     <t>DOINA.ATANASOAEI</t>
   </si>
   <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>JANE.LUCIANO</t>
+  </si>
+  <si>
+    <t>DI DEO MICHELE</t>
+  </si>
+  <si>
+    <t>PACELLA VALERY</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>DI LANZO ALESSIO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DAVIDE.DI CRISTOFARO</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>JANE.LUCIANO</t>
-  </si>
-  <si>
-    <t>DI DEO MICHELE</t>
-  </si>
-  <si>
-    <t>PACELLA VALERY</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>DI LANZO ALESSIO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CHRISTIAN.VERNA</t>
-  </si>
-  <si>
-    <t>GIOBBE MICHELE</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1030,7 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1071,7 +1068,7 @@
         <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1122,7 +1119,7 @@
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1157,7 +1154,7 @@
         <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1168,7 +1165,7 @@
         <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1179,7 +1176,7 @@
         <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1198,7 +1195,7 @@
         <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1265,7 +1262,7 @@
         <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1372,7 +1369,7 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1447,7 +1444,7 @@
         <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1479,7 +1476,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>125</v>
+      </c>
+      <c r="C55" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1487,7 +1487,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1495,7 +1495,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1503,7 +1503,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1511,7 +1511,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1519,10 +1519,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1530,7 +1530,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1538,7 +1538,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1546,7 +1546,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1554,7 +1554,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1562,7 +1562,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1570,7 +1570,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1578,7 +1578,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1586,7 +1586,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1594,7 +1594,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1602,7 +1602,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1610,7 +1610,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1618,7 +1618,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
         <v>199</v>
@@ -1629,7 +1629,7 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1637,7 +1637,7 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
         <v>200</v>
@@ -1648,10 +1648,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1659,10 +1659,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1670,7 +1670,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1678,7 +1678,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1686,7 +1686,7 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
         <v>199</v>
@@ -1697,7 +1697,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1705,7 +1705,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1713,7 +1713,7 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
         <v>201</v>
@@ -1724,7 +1724,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1732,7 +1732,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1740,7 +1740,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1756,7 +1756,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1764,7 +1764,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1772,7 +1772,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1780,7 +1780,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1788,7 +1788,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1804,7 +1804,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1812,7 +1812,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1855,7 +1855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1874,30 +1874,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>207</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F9A7577B2C2024111FF23C8B296EB7DE7A1F5781" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF9CE68-7F06-4E18-BCB1-6F080F9CEA39}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
   <si>
     <t>targa</t>
   </si>
@@ -639,16 +645,22 @@
   </si>
   <si>
     <t>DAVIDE.DI CRISTOFARO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL352TJ </t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,17 +720,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -756,7 +776,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -790,6 +810,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -824,9 +845,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -999,11 +1021,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="55.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1014,7 +1039,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1022,7 +1047,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1033,7 +1058,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1041,7 +1066,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1049,7 +1074,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1060,7 +1085,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1071,7 +1096,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1079,7 +1104,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1087,7 +1112,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1095,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1103,7 +1128,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1136,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1122,7 +1147,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1130,7 +1155,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1138,7 +1163,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1146,7 +1171,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -1157,7 +1182,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1168,7 +1193,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -1179,7 +1204,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1187,7 +1212,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -1198,7 +1223,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1206,7 +1231,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -1214,7 +1239,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -1222,7 +1247,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1230,7 +1255,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1238,7 +1263,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -1246,7 +1271,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -1254,7 +1279,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -1265,7 +1290,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1273,7 +1298,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -1281,7 +1306,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1289,7 +1314,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -1297,7 +1322,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -1305,7 +1330,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -1313,7 +1338,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -1321,7 +1346,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -1329,7 +1354,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -1337,7 +1362,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1345,7 +1370,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -1353,7 +1378,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -1361,7 +1386,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1372,7 +1397,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -1380,7 +1405,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -1388,7 +1413,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -1396,7 +1421,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -1404,7 +1429,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -1412,7 +1437,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -1420,7 +1445,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -1428,7 +1453,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -1436,7 +1461,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -1447,7 +1472,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -1455,7 +1480,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -1463,7 +1488,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -1471,7 +1496,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -1482,7 +1507,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -1490,7 +1515,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -1498,7 +1523,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -1506,7 +1531,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -1514,7 +1539,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -1525,7 +1550,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -1533,7 +1558,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -1541,7 +1566,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -1549,7 +1574,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -1557,7 +1582,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -1565,7 +1590,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -1573,7 +1598,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -1581,7 +1606,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -1589,7 +1614,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -1597,7 +1622,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -1605,7 +1630,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -1613,7 +1638,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -1624,7 +1649,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -1632,7 +1657,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1643,7 +1668,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1654,7 +1679,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1665,7 +1690,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1673,7 +1698,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1681,7 +1706,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1692,7 +1717,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1700,7 +1725,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1708,7 +1733,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1719,7 +1744,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1727,7 +1752,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1735,7 +1760,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1743,7 +1768,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1751,7 +1776,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1759,7 +1784,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1767,7 +1792,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1775,7 +1800,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1783,7 +1808,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1791,7 +1816,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1799,7 +1824,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1807,7 +1832,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1815,7 +1840,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -1826,7 +1851,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -1837,7 +1862,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -1846,6 +1871,14 @@
       </c>
       <c r="C97" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -1854,11 +1887,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>203</v>
       </c>
@@ -1872,7 +1905,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>56</v>
       </c>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://domyssrl-my.sharepoint.com/personal/acquisti_domys_it/Documents/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F9A7577B2C2024111FF23C8B296EB7DE7A1F5781" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF9CE68-7F06-4E18-BCB1-6F080F9CEA39}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Stato Attuale" sheetId="1" r:id="rId1"/>
     <sheet name="Storico Passaggi" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="211">
   <si>
     <t>targa</t>
   </si>
@@ -320,6 +314,9 @@
     <t>GX666SK</t>
   </si>
   <si>
+    <t>GL352TJ</t>
+  </si>
+  <si>
     <t>RUSSO.ZAIRA</t>
   </si>
   <si>
@@ -374,293 +371,293 @@
     <t>DAVIDE.BONFITTO</t>
   </si>
   <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>DI DEO MICHELE</t>
+  </si>
+  <si>
+    <t>PACELLA VALERY</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>DI LANZO ALESSIO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>CENTRO DAMA (JANE QUANDO RIENTRA)</t>
   </si>
   <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
     <t>JANE.LUCIANO</t>
-  </si>
-  <si>
-    <t>DI DEO MICHELE</t>
-  </si>
-  <si>
-    <t>PACELLA VALERY</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>DI LANZO ALESSIO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DAVIDE.DI CRISTOFARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GL352TJ </t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,25 +717,17 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -776,7 +765,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -810,7 +799,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -845,10 +833,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1021,14 +1008,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="55.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1039,80 +1023,80 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2">
         <v>45851</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1120,544 +1104,547 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="C73" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -1665,10 +1652,10 @@
         <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -1676,10 +1663,10 @@
         <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -1687,10 +1674,10 @@
         <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -1698,7 +1685,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -1706,7 +1693,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -1714,10 +1701,10 @@
         <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -1725,7 +1712,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -1733,7 +1720,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -1741,10 +1728,10 @@
         <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -1752,7 +1739,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -1760,7 +1747,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -1768,7 +1755,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -1776,7 +1763,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -1784,7 +1771,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -1792,7 +1779,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -1800,7 +1787,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -1808,7 +1795,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -1816,7 +1803,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -1824,7 +1811,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -1832,7 +1819,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -1840,45 +1827,45 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1887,36 +1874,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="210">
   <si>
     <t>targa</t>
   </si>
@@ -365,289 +365,286 @@
     <t>PARDI ELIANA</t>
   </si>
   <si>
+    <t>FRANCESCO COCCHIARA</t>
+  </si>
+  <si>
+    <t>DAVIDE.BONFITTO</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>DI DEO MICHELE</t>
+  </si>
+  <si>
+    <t>PACELLA VALERY</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>DI LANZO ALESSIO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE(MANDARE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DAVIDE.BONFITTO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>DI DEO MICHELE</t>
-  </si>
-  <si>
-    <t>PACELLA VALERY</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>DI LANZO ALESSIO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CENTRO DAMA (JANE QUANDO RIENTRA)</t>
-  </si>
-  <si>
-    <t>JANE.LUCIANO</t>
   </si>
 </sst>
 </file>
@@ -1204,7 +1201,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1271,7 +1268,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1453,7 +1450,7 @@
         <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1488,7 +1485,7 @@
         <v>126</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1630,7 +1627,7 @@
         <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1641,7 +1638,7 @@
         <v>126</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1652,7 +1649,7 @@
         <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1674,7 +1671,7 @@
         <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1701,7 +1698,7 @@
         <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1846,7 +1843,7 @@
         <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1875,7 +1872,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1894,30 +1891,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="210">
   <si>
     <t>targa</t>
   </si>
@@ -362,289 +362,289 @@
     <t>ELENA DELL'ARCIPRETE</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>FRANCESCO COCCHIARA</t>
+  </si>
+  <si>
+    <t>DAVIDE.BONFITTO</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>DI DEO MICHELE</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>DI LANZO ALESSIO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>PARDI ELIANA</t>
   </si>
   <si>
-    <t>FRANCESCO COCCHIARA</t>
-  </si>
-  <si>
-    <t>DAVIDE.BONFITTO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>DI DEO MICHELE</t>
-  </si>
-  <si>
     <t>PACELLA VALERY</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>DI LANZO ALESSIO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE(MANDARE IN ASSISTENZA)</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1036,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1074,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1160,7 +1160,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1171,7 +1171,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1182,7 +1182,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1201,7 +1201,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1265,10 +1265,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1276,7 +1276,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1284,7 +1284,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1292,7 +1292,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1308,7 +1308,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1316,7 +1316,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1324,7 +1324,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1332,7 +1332,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1340,7 +1340,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1348,7 +1348,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1356,7 +1356,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1364,7 +1364,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1372,10 +1372,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1383,7 +1383,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1391,7 +1391,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1399,7 +1399,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1407,7 +1407,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1415,7 +1415,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1423,7 +1423,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1431,7 +1431,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1439,7 +1439,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1447,10 +1447,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1458,7 +1458,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1466,7 +1466,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1474,7 +1474,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1482,10 +1482,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1493,7 +1493,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1501,7 +1501,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1509,7 +1509,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1517,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1525,10 +1525,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1536,7 +1536,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1544,7 +1544,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1552,7 +1552,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1560,7 +1560,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1568,7 +1568,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1576,7 +1576,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1584,7 +1584,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1592,7 +1592,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1600,7 +1600,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1608,7 +1608,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1616,7 +1616,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1624,10 +1624,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1635,10 +1635,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1646,10 +1646,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1657,7 +1657,7 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
         <v>194</v>
@@ -1668,10 +1668,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1679,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1687,7 +1687,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1695,10 +1695,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1706,7 +1706,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1714,7 +1714,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1722,10 +1722,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1733,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1749,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1765,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1773,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1781,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1813,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1821,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1829,10 +1829,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1840,10 +1840,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1851,10 +1851,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1862,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1872,35 +1872,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" t="s">
         <v>209</v>
       </c>
-      <c r="C2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" t="s">
-        <v>196</v>
+      <c r="C3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="208">
   <si>
     <t>targa</t>
   </si>
@@ -545,106 +545,100 @@
     <t>MARCO.DI.NIZO</t>
   </si>
   <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-10</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DI LANZO ALESSIO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>PARDI ELIANA</t>
-  </si>
-  <si>
-    <t>PACELLA VALERY</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1030,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1068,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1125,7 +1119,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1160,7 +1154,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1171,7 +1165,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1182,7 +1176,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1201,7 +1195,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1268,7 +1262,7 @@
         <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1375,7 +1369,7 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1450,7 +1444,7 @@
         <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1485,7 +1479,7 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1528,7 +1522,7 @@
         <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1627,7 +1621,7 @@
         <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1638,7 +1632,7 @@
         <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1649,7 +1643,7 @@
         <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1660,7 +1654,7 @@
         <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1671,7 +1665,7 @@
         <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1698,7 +1692,7 @@
         <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1722,10 +1716,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1727,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1735,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1743,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1751,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1759,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1767,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1775,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1783,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1791,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1799,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1807,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1815,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1832,7 +1826,7 @@
         <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1843,7 +1837,7 @@
         <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1854,7 +1848,7 @@
         <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1856,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1872,49 +1866,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C2" t="s">
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="206">
   <si>
     <t>targa</t>
   </si>
@@ -395,6 +395,9 @@
     <t>MICAELA.POSTIGLIONE</t>
   </si>
   <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
     <t>ARSONELA-MUCA</t>
   </si>
   <si>
@@ -518,9 +521,6 @@
     <t>TONIA DE TOMMASO</t>
   </si>
   <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
     <t>DI DEO MICHELE</t>
   </si>
   <si>
@@ -602,7 +602,7 @@
     <t>2026-02-24</t>
   </si>
   <si>
-    <t>2026-02-10</t>
+    <t>2026-03-06</t>
   </si>
   <si>
     <t>2026-01-09</t>
@@ -611,18 +611,15 @@
     <t>2026-02-18</t>
   </si>
   <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
     <t>2026-01-28</t>
   </si>
   <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>2025-12-18</t>
   </si>
   <si>
@@ -636,9 +633,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DI LANZO ALESSIO</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1253,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
         <v>195</v>
@@ -1270,7 +1264,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1278,7 +1272,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1286,7 +1280,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1294,7 +1288,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1302,7 +1296,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1310,7 +1304,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1318,7 +1312,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1326,7 +1320,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1334,7 +1328,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1342,7 +1336,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1350,7 +1344,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1358,7 +1352,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1366,7 +1360,7 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
         <v>191</v>
@@ -1377,7 +1371,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1385,7 +1379,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1393,7 +1387,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1401,7 +1395,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1409,7 +1403,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1417,7 +1411,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1425,7 +1419,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1433,7 +1427,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1441,7 +1435,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
         <v>196</v>
@@ -1452,7 +1446,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1460,7 +1454,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1468,7 +1462,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1487,7 +1481,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1495,7 +1489,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1503,7 +1497,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1511,7 +1505,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1519,7 +1513,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
         <v>190</v>
@@ -1530,7 +1524,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1538,7 +1532,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1546,7 +1540,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1554,7 +1548,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1562,7 +1556,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1570,7 +1564,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1578,7 +1572,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1586,7 +1580,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1594,7 +1588,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1602,7 +1596,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1610,7 +1604,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1618,10 +1612,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>115</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1643,7 +1637,7 @@
         <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1665,7 +1659,7 @@
         <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1692,7 +1686,7 @@
         <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1719,7 +1713,7 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1823,10 +1817,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1834,10 +1828,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1845,10 +1839,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1866,35 +1860,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="208">
   <si>
     <t>targa</t>
   </si>
@@ -521,6 +521,9 @@
     <t>TONIA DE TOMMASO</t>
   </si>
   <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
     <t>DI DEO MICHELE</t>
   </si>
   <si>
@@ -609,6 +612,9 @@
   </si>
   <si>
     <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
   </si>
   <si>
     <t>2026-02-13</t>
@@ -1024,7 +1030,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1062,7 +1068,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1113,7 +1119,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1148,7 +1154,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1159,7 +1165,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1170,7 +1176,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1189,7 +1195,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1256,7 +1262,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1363,7 +1369,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1438,7 +1444,7 @@
         <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1473,7 +1479,7 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1516,7 +1522,7 @@
         <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1612,10 +1618,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1626,7 +1632,7 @@
         <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1634,10 +1640,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1645,10 +1651,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1656,10 +1662,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1667,7 +1673,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1675,7 +1681,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1683,10 +1689,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1694,7 +1700,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1702,7 +1708,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1713,7 +1719,7 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1721,7 +1727,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1729,7 +1735,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1737,7 +1743,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1745,7 +1751,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1753,7 +1759,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1761,7 +1767,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1769,7 +1775,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1777,7 +1783,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1785,7 +1791,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1793,7 +1799,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1801,7 +1807,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1809,7 +1815,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1820,7 +1826,7 @@
         <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1831,7 +1837,7 @@
         <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1842,7 +1848,7 @@
         <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1850,7 +1856,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1860,21 +1866,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1882,27 +1888,13 @@
         <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="209">
   <si>
     <t>targa</t>
   </si>
@@ -624,6 +624,9 @@
   </si>
   <si>
     <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>2025-12-18</t>
@@ -1719,7 +1722,7 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1826,7 +1829,7 @@
         <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1848,7 +1851,7 @@
         <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1871,30 +1874,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="210">
   <si>
     <t>targa</t>
   </si>
@@ -524,124 +524,127 @@
     <t>BENEGIAMO VALERIA</t>
   </si>
   <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-01-05</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DI DEO MICHELE</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1036,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1071,7 +1074,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1122,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1157,7 +1160,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1168,7 +1171,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1179,7 +1182,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1198,7 +1201,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1265,7 +1268,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1372,7 +1375,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1447,7 +1450,7 @@
         <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1482,7 +1485,7 @@
         <v>115</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1525,7 +1528,7 @@
         <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1624,7 +1627,7 @@
         <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1635,7 +1638,7 @@
         <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1643,10 +1646,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1654,10 +1657,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1665,10 +1668,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1676,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1684,7 +1687,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1692,10 +1695,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1703,7 +1706,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1711,7 +1714,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1722,7 +1725,7 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1730,7 +1733,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1738,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1746,7 +1749,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1754,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1762,7 +1765,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1770,7 +1773,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1778,7 +1781,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1786,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1794,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1802,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1810,7 +1813,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1818,7 +1821,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1829,7 +1832,7 @@
         <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1840,7 +1843,7 @@
         <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1851,7 +1854,7 @@
         <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1859,7 +1862,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1888,16 +1891,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
         <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -473,6 +473,9 @@
     <t>DOINA.ATANASOAEI</t>
   </si>
   <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
     <t>FRANCESCO.DI.DOMENICANTONIO</t>
   </si>
   <si>
@@ -608,7 +611,7 @@
     <t>2026-01-09</t>
   </si>
   <si>
-    <t>2026-02-18</t>
+    <t>2026-03-23</t>
   </si>
   <si>
     <t>2026-03-09</t>
@@ -642,9 +645,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DI DEO MICHELE</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1036,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1074,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1160,7 +1160,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1171,7 +1171,7 @@
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1182,7 +1182,7 @@
         <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1201,7 +1201,7 @@
         <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1268,7 +1268,7 @@
         <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1375,7 +1375,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1450,7 +1450,7 @@
         <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1482,10 +1482,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1493,7 +1493,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1501,7 +1501,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1509,7 +1509,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1517,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1525,10 +1525,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1536,7 +1536,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1544,7 +1544,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1552,7 +1552,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1560,7 +1560,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1568,7 +1568,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1576,7 +1576,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1584,7 +1584,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1592,7 +1592,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1600,7 +1600,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1608,7 +1608,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1616,7 +1616,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1624,10 +1624,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1638,7 +1638,7 @@
         <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1649,7 +1649,7 @@
         <v>115</v>
       </c>
       <c r="C74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1657,10 +1657,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1668,10 +1668,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1679,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1687,7 +1687,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1695,10 +1695,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1706,7 +1706,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1714,7 +1714,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1725,7 +1725,7 @@
         <v>115</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1733,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1749,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1765,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1773,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1781,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1813,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1821,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1832,7 +1832,7 @@
         <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1843,7 +1843,7 @@
         <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1854,7 +1854,7 @@
         <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1862,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1877,30 +1877,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -320,331 +320,331 @@
     <t>RUSSO.ZAIRA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>STEFANO.CAMPLONE</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>ZACCAGNIGNO ROCCO</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
+  </si>
+  <si>
+    <t>ALEMANNO.PIERPAOLO 28-07 TEMPORANEO</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>ELENA DELL'ARCIPRETE</t>
+  </si>
+  <si>
+    <t>FRANCESCO COCCHIARA</t>
+  </si>
+  <si>
+    <t>DAVIDE.BONFITTO</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-01-12</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>MEZZANOTTE SABRINA</t>
-  </si>
-  <si>
-    <t>STEFANO.CAMPLONE</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>ZACCAGNIGNO ROCCO</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
-  </si>
-  <si>
-    <t>ALEMANNO.PIERPAOLO 28-07 TEMPORANEO</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>ELENA DELL'ARCIPRETE</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>FRANCESCO COCCHIARA</t>
-  </si>
-  <si>
-    <t>DAVIDE.BONFITTO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1036,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1074,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1160,7 +1160,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1168,10 +1168,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1179,10 +1179,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1190,7 +1190,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1198,10 +1198,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1209,7 +1209,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1217,7 +1217,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1225,7 +1225,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1233,7 +1233,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1241,7 +1241,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1249,7 +1249,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1257,7 +1257,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1265,10 +1265,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1276,7 +1276,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1284,7 +1284,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1292,7 +1292,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1300,7 +1300,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1308,7 +1308,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1316,7 +1316,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1324,7 +1324,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1332,7 +1332,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1340,7 +1340,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1348,7 +1348,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1356,7 +1356,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1364,7 +1364,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1372,10 +1372,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1383,7 +1383,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1391,7 +1391,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1399,7 +1399,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1407,7 +1407,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1415,7 +1415,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1423,7 +1423,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1431,7 +1431,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1439,7 +1439,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1447,10 +1447,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1458,7 +1458,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1466,7 +1466,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1474,7 +1474,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1482,10 +1482,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1493,7 +1493,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1501,7 +1501,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1509,7 +1509,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1517,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1525,10 +1525,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1536,7 +1536,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1544,7 +1544,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1552,7 +1552,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1560,7 +1560,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1568,7 +1568,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1576,7 +1576,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1584,7 +1584,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1592,7 +1592,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1600,7 +1600,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1608,7 +1608,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1616,7 +1616,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1624,10 +1624,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1635,10 +1635,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1646,10 +1646,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1657,10 +1657,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1668,10 +1668,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1679,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1687,7 +1687,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1695,10 +1695,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1706,7 +1706,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1714,7 +1714,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1722,10 +1722,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1733,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1749,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1765,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1773,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1781,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1813,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1821,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1829,10 +1829,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1840,10 +1840,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1851,10 +1851,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1862,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -1877,30 +1877,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -545,6 +545,9 @@
     <t>MARCO.DI.NIZO</t>
   </si>
   <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
     <t>SARA.VALLERI</t>
   </si>
   <si>
@@ -623,7 +626,7 @@
     <t>2026-01-28</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-03-30</t>
   </si>
   <si>
     <t>2025-12-18</t>
@@ -642,9 +645,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MEZZANOTTE SABRINA</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1036,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1074,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1125,7 +1125,7 @@
         <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1160,7 +1160,7 @@
         <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1171,7 +1171,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1182,7 +1182,7 @@
         <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1201,7 +1201,7 @@
         <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1268,7 +1268,7 @@
         <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1375,7 +1375,7 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1450,7 +1450,7 @@
         <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1485,7 +1485,7 @@
         <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1528,7 +1528,7 @@
         <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1627,7 +1627,7 @@
         <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1638,7 +1638,7 @@
         <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1649,7 +1649,7 @@
         <v>101</v>
       </c>
       <c r="C74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1660,7 +1660,7 @@
         <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1671,7 +1671,7 @@
         <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1698,7 +1698,7 @@
         <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1722,10 +1722,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1733,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1749,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1757,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1765,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1773,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1781,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1797,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1813,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1821,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1832,7 +1832,7 @@
         <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1843,7 +1843,7 @@
         <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1854,7 +1854,7 @@
         <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1862,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -1877,30 +1877,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="211">
   <si>
     <t>targa</t>
   </si>
@@ -341,6 +341,9 @@
     <t>VALERY.PACELLA</t>
   </si>
   <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
     <t>SIMONA.PETRAGNANO</t>
   </si>
   <si>
@@ -593,6 +596,9 @@
     <t>2025-12-19</t>
   </si>
   <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
     <t>2026-01-29</t>
   </si>
   <si>
@@ -624,9 +630,6 @@
   </si>
   <si>
     <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
   </si>
   <si>
     <t>2025-12-18</t>
@@ -1036,7 +1039,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1074,7 +1077,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1097,8 +1100,11 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>0</v>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1106,7 +1112,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1114,7 +1120,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1122,10 +1128,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1133,7 +1139,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1141,7 +1147,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1149,7 +1155,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1157,10 +1163,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1171,7 +1177,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1179,10 +1185,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1190,7 +1196,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1198,10 +1204,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1209,7 +1215,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1217,7 +1223,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1225,7 +1231,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1233,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1241,7 +1247,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1249,7 +1255,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1257,7 +1263,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1265,10 +1271,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1276,7 +1282,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1284,7 +1290,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1292,7 +1298,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1300,7 +1306,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1308,7 +1314,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1316,7 +1322,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1324,7 +1330,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1332,7 +1338,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1340,7 +1346,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1348,7 +1354,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1356,7 +1362,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1364,7 +1370,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1372,10 +1378,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1383,7 +1389,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1391,7 +1397,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1399,7 +1405,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1407,7 +1413,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1415,7 +1421,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1423,7 +1429,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1431,7 +1437,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1439,7 +1445,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1447,10 +1453,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1458,7 +1464,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1466,7 +1472,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1474,7 +1480,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1482,10 +1488,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1493,7 +1499,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1501,7 +1507,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1509,7 +1515,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1517,7 +1523,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1525,10 +1531,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1536,7 +1542,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1544,7 +1550,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1552,7 +1558,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1560,7 +1566,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1568,7 +1574,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1576,7 +1582,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1584,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1592,7 +1598,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1600,7 +1606,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1608,7 +1614,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1616,7 +1622,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1624,10 +1630,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1638,7 +1644,7 @@
         <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1649,7 +1655,7 @@
         <v>101</v>
       </c>
       <c r="C74" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1657,10 +1663,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1668,10 +1674,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1679,7 +1685,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1687,7 +1693,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1695,10 +1701,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1706,7 +1712,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1714,7 +1720,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1722,10 +1728,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1733,7 +1739,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1741,7 +1747,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1749,7 +1755,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1757,7 +1763,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1765,7 +1771,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1773,7 +1779,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1781,7 +1787,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1789,7 +1795,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1797,7 +1803,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1805,7 +1811,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1813,7 +1819,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1821,7 +1827,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1829,10 +1835,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1840,10 +1846,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1851,10 +1857,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1862,7 +1868,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1877,30 +1883,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" t="s">
-        <v>101</v>
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="212">
   <si>
     <t>targa</t>
   </si>
@@ -362,292 +362,295 @@
     <t>DI TIZIO.VALENTINA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
+  </si>
+  <si>
+    <t>DAVIDE.BONFITTO</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MOMENTANEAMENTE MATTEO CERRITELLI)</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>FRANCESCO COCCHIARA</t>
+  </si>
+  <si>
     <t>ELENA DELL'ARCIPRETE</t>
-  </si>
-  <si>
-    <t>FRANCESCO COCCHIARA</t>
-  </si>
-  <si>
-    <t>DAVIDE.BONFITTO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -657,16 +660,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -682,7 +677,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -690,30 +685,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1013,13 +990,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1065,7 +1042,7 @@
       <c r="B6" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>45851</v>
       </c>
     </row>
@@ -1185,10 +1162,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1196,7 +1173,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1204,7 +1181,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
         <v>197</v>
@@ -1215,7 +1192,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1223,7 +1200,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1231,7 +1208,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1239,7 +1216,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1247,7 +1224,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1255,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1263,7 +1240,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1271,7 +1248,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
         <v>198</v>
@@ -1282,7 +1259,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1290,7 +1267,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1298,7 +1275,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1306,7 +1283,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1314,7 +1291,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1322,7 +1299,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1330,7 +1307,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1338,7 +1315,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1346,7 +1323,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1354,7 +1331,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1362,7 +1339,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1370,7 +1347,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1378,7 +1355,7 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
         <v>194</v>
@@ -1389,7 +1366,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1397,7 +1374,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1405,7 +1382,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1413,7 +1390,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1421,7 +1398,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1429,7 +1406,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1437,7 +1414,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1445,7 +1422,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1453,7 +1430,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
         <v>199</v>
@@ -1464,7 +1441,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1472,7 +1449,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1480,7 +1457,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1488,7 +1465,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
         <v>200</v>
@@ -1499,7 +1476,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1507,7 +1484,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1515,7 +1492,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1523,7 +1500,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1531,7 +1508,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
         <v>192</v>
@@ -1542,7 +1519,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1550,7 +1527,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1558,7 +1535,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1566,7 +1543,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1574,7 +1551,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1582,7 +1559,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1590,7 +1567,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1598,7 +1575,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1606,7 +1583,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1614,7 +1591,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1622,7 +1599,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1630,7 +1607,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
         <v>201</v>
@@ -1652,10 +1629,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1677,7 +1654,7 @@
         <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1704,7 +1681,7 @@
         <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1835,10 +1812,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1846,10 +1823,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1857,10 +1834,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1878,35 +1855,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>208</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" t="s">
         <v>209</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="212">
   <si>
     <t>targa</t>
   </si>
@@ -524,133 +524,133 @@
     <t>BENEGIAMO VALERIA</t>
   </si>
   <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>TEODORO DE MARCO</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE (MOMENTANEAMENTE MATTEO CERRITELLI)</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>FRANCESCO COCCHIARA</t>
-  </si>
-  <si>
-    <t>ELENA DELL'ARCIPRETE</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1016,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1054,7 +1054,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1081,7 +1081,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1108,7 +1108,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1143,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1154,7 +1154,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1165,7 +1165,7 @@
         <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1184,7 +1184,7 @@
         <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1251,7 +1251,7 @@
         <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1358,7 +1358,7 @@
         <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1433,7 +1433,7 @@
         <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1468,7 +1468,7 @@
         <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1511,7 +1511,7 @@
         <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1610,7 +1610,7 @@
         <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1621,7 +1621,7 @@
         <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1629,10 +1629,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1640,10 +1640,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1651,7 +1651,7 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
         <v>202</v>
@@ -1662,7 +1662,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1670,7 +1670,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1678,7 +1678,7 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
         <v>203</v>
@@ -1689,7 +1689,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1697,7 +1697,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1705,10 +1705,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1716,7 +1716,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1724,7 +1724,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1732,7 +1732,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1740,7 +1740,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1748,7 +1748,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1756,7 +1756,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1764,7 +1764,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1772,7 +1772,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1780,7 +1780,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1788,7 +1788,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1796,7 +1796,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1804,7 +1804,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1845,7 +1845,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>189</v>
+      </c>
+      <c r="C98" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +1858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1874,44 +1877,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
         <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="214">
   <si>
     <t>targa</t>
   </si>
@@ -365,292 +365,298 @@
     <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
   </si>
   <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>BRAGHINI MATTEO</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DAVIDE.BONFITTO</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>TEODORO DE MARCO</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MOMENTANEAMENTE MATTEO CERRITELLI)</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1022,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1054,7 +1060,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1081,7 +1087,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1108,7 +1114,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1143,7 +1149,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1151,10 +1157,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1162,10 +1168,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1173,7 +1179,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1181,10 +1190,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1192,7 +1201,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1200,7 +1209,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1208,7 +1217,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1216,7 +1225,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1224,7 +1233,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1232,7 +1241,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1240,7 +1249,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1248,10 +1257,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1259,7 +1268,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1267,7 +1276,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1275,7 +1284,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1283,7 +1292,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1291,7 +1300,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1299,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1307,7 +1316,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1315,7 +1324,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1323,7 +1332,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1331,7 +1340,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1339,7 +1348,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1347,7 +1356,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1355,10 +1364,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1366,7 +1375,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1374,7 +1383,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1382,7 +1391,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1390,7 +1399,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1398,7 +1407,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1406,7 +1415,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1414,7 +1423,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1422,7 +1431,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1430,10 +1439,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1441,7 +1450,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1449,7 +1458,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1457,7 +1466,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1465,10 +1474,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1476,7 +1485,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1484,7 +1493,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1492,7 +1501,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1500,7 +1509,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1508,10 +1517,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1519,7 +1528,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1527,7 +1536,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1535,7 +1544,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1543,7 +1552,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1551,7 +1560,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1559,7 +1568,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1567,7 +1576,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1575,7 +1584,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1583,7 +1592,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1591,7 +1600,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1599,7 +1608,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1607,10 +1616,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1621,7 +1630,7 @@
         <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1629,10 +1638,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1640,10 +1649,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1651,10 +1660,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1662,7 +1671,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1670,7 +1679,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1678,10 +1687,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1689,7 +1698,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1697,7 +1706,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1705,10 +1714,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1716,7 +1725,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1724,7 +1733,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1732,7 +1741,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1740,7 +1749,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1748,7 +1757,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1756,7 +1765,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1764,7 +1773,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1772,7 +1781,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1780,7 +1789,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1788,7 +1797,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1796,7 +1805,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1804,7 +1813,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1812,10 +1821,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1823,10 +1832,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1834,10 +1843,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1845,10 +1854,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1858,49 +1867,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>201</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="214">
   <si>
     <t>targa</t>
   </si>
@@ -398,265 +398,265 @@
     <t>MICAELA.POSTIGLIONE</t>
   </si>
   <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>BRAGHINI MATTEO</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DAVIDE.BONFITTO</t>
   </si>
 </sst>
 </file>
@@ -1867,7 +1867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1886,44 +1886,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>213</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="215">
   <si>
     <t>targa</t>
   </si>
@@ -353,310 +353,313 @@
     <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
   </si>
   <si>
+    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>ARSONELA-MUCA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>NOD PESCARA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>ALEMANNO.PIERPAOLO 28-07 TEMPORANEO</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>BRAGHINI MATTEO</t>
   </si>
 </sst>
 </file>
@@ -1124,6 +1127,9 @@
       <c r="B14" t="s">
         <v>112</v>
       </c>
+      <c r="C14" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
@@ -1149,7 +1155,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1160,7 +1166,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1171,7 +1177,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1182,7 +1188,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1193,7 +1199,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1260,7 +1266,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1442,7 +1448,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1477,7 +1483,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1619,7 +1625,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1630,7 +1636,7 @@
         <v>101</v>
       </c>
       <c r="C73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1641,7 +1647,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1652,7 +1658,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1663,7 +1669,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1690,7 +1696,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1824,7 +1830,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1835,7 +1841,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1846,7 +1852,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1857,7 +1863,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1872,30 +1878,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="214">
   <si>
     <t>targa</t>
   </si>
@@ -657,9 +657,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ALEMANNO.PIERPAOLO 28-07 TEMPORANEO</t>
   </si>
 </sst>
 </file>
@@ -1633,10 +1630,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1892,13 +1889,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
         <v>196</v>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="216">
   <si>
     <t>targa</t>
   </si>
@@ -461,202 +461,208 @@
     <t>SIMONA.TURDò</t>
   </si>
   <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>NOD PESCARA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1436,6 +1442,9 @@
       <c r="B50" t="s">
         <v>148</v>
       </c>
+      <c r="C50" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
@@ -1445,7 +1454,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1480,7 +1489,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1622,7 +1631,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1644,7 +1653,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1655,7 +1664,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1666,7 +1675,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1693,7 +1702,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1827,7 +1836,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1838,7 +1847,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1849,7 +1858,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1860,7 +1869,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1875,30 +1884,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="215">
   <si>
     <t>targa</t>
   </si>
@@ -551,118 +551,115 @@
     <t>MARCO.DI.NIZO</t>
   </si>
   <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>NOD PESCARA</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1025,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1066,7 +1063,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1093,7 +1090,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1120,7 +1117,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1131,7 +1128,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1158,7 +1155,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1169,7 +1166,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1180,7 +1177,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1191,7 +1188,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1202,7 +1199,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1269,7 +1266,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1376,7 +1373,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1443,7 +1440,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1454,7 +1451,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1489,7 +1486,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1532,7 +1529,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1631,7 +1628,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1642,7 +1639,7 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1653,7 +1650,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1664,7 +1661,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1675,7 +1672,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1702,7 +1699,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1726,10 +1723,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1737,7 +1734,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1745,7 +1742,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1753,7 +1750,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1761,7 +1758,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1769,7 +1766,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1777,7 +1774,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1785,7 +1782,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1793,7 +1790,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1801,7 +1798,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1809,7 +1806,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1817,7 +1814,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1825,7 +1822,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1836,7 +1833,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1847,7 +1844,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1858,7 +1855,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1866,10 +1863,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -1884,30 +1881,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" t="s">
         <v>211</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>212</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>213</v>
-      </c>
-      <c r="D1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="217">
   <si>
     <t>targa</t>
   </si>
@@ -365,301 +365,307 @@
     <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
   </si>
   <si>
+    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CELA REZEARTA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
-    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
   </si>
   <si>
     <t>ARSONELA-MUCA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>D'ANTONIO VALERIO (FURGONE IN ASSISTENZA)</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1031,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1063,7 +1069,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1090,7 +1096,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1117,7 +1123,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1128,7 +1134,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1155,7 +1161,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1166,7 +1172,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1177,7 +1183,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1188,7 +1194,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1199,7 +1205,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1266,7 +1272,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1276,6 +1282,9 @@
       <c r="B30" t="s">
         <v>128</v>
       </c>
+      <c r="C30" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
@@ -1373,7 +1382,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1440,7 +1449,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1451,7 +1460,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1486,7 +1495,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1529,7 +1538,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1628,7 +1637,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1639,7 +1648,7 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1650,7 +1659,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1661,7 +1670,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1672,7 +1681,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1699,7 +1708,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1723,10 +1732,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1734,7 +1743,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1742,7 +1751,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1750,7 +1759,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1758,7 +1767,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1766,7 +1775,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1774,7 +1783,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1782,7 +1791,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1790,7 +1799,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1798,7 +1807,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1806,7 +1815,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1814,7 +1823,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1822,7 +1831,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1833,7 +1842,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1844,7 +1853,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1855,7 +1864,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1863,10 +1872,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -1876,35 +1885,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>83</v>
       </c>
-      <c r="B2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
-      <c r="D2" t="s">
-        <v>200</v>
+      <c r="C3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="218">
   <si>
     <t>targa</t>
   </si>
@@ -368,304 +368,307 @@
     <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
   </si>
   <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CELA REZEARTA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CELA REZEARTA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ARSONELA-MUCA</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1197,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1205,7 +1208,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1272,7 +1275,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1449,7 +1452,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1460,7 +1463,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1495,7 +1498,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1637,7 +1640,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1659,7 +1662,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1670,7 +1673,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1681,7 +1684,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1708,7 +1711,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1842,7 +1845,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1853,7 +1856,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1864,7 +1867,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1875,7 +1878,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -1885,63 +1888,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="219">
   <si>
     <t>targa</t>
   </si>
@@ -332,343 +332,346 @@
     <t>TELEASA GEANINA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
+  </si>
+  <si>
+    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CELA REZEARTA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>ZACCAGNIGNO ROCCO</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
-  </si>
-  <si>
-    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CELA REZEARTA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>BOVE NATHALIE (LA SUA IN ASSISTENZA)</t>
   </si>
 </sst>
 </file>
@@ -1541,7 +1544,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1640,7 +1643,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1662,7 +1665,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1673,7 +1676,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1684,7 +1687,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1711,7 +1714,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1845,7 +1848,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1856,7 +1859,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1867,7 +1870,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1878,7 +1881,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1893,30 +1896,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="221">
   <si>
     <t>targa</t>
   </si>
@@ -350,328 +350,334 @@
     <t>ALESSIA.DE LUCA</t>
   </si>
   <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CELA REZEARTA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA PATERNITA' - FERMA A LANCIANO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
+    <t>SARA.VALLERI</t>
+  </si>
+  <si>
+    <t>LELLA DARIO</t>
+  </si>
+  <si>
     <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
-  </si>
-  <si>
-    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CELA REZEARTA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ZACCAGNIGNO ROCCO</t>
   </si>
 </sst>
 </file>
@@ -1751,6 +1757,9 @@
       <c r="B83" t="s">
         <v>179</v>
       </c>
+      <c r="C83" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" t="s">
@@ -1891,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1910,16 +1919,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="219">
   <si>
     <t>targa</t>
   </si>
@@ -362,322 +362,316 @@
     <t>DI TIZIO.VALENTINA</t>
   </si>
   <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CELA REZEARTA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>LELLA PATERNITA' - FERMA A LANCIANO</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CELA REZEARTA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>LELLA PATERNITA' - FERMA A LANCIANO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>SARA.VALLERI</t>
-  </si>
-  <si>
-    <t>LELLA DARIO</t>
-  </si>
-  <si>
-    <t>LELLA DARIO (INCIDENTATA FARE PRATICA - DECUNCIA CC)</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1919,44 +1913,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
         <v>218</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="220">
   <si>
     <t>targa</t>
   </si>
@@ -437,241 +437,244 @@
     <t>LEPORATI PEREZ.MELANY LUNA</t>
   </si>
   <si>
+    <t>ALIAJ.KLODIAN (TEMPORANEAMENTE PER TAGLIANDO)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>SOFIA.D'ANGELO</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>LELLA PATERNITA' - FERMA A LANCIANO</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (SENTIRE ERIKA)</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1391,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1455,7 +1458,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1466,7 +1469,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1501,7 +1504,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1544,7 +1547,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1643,7 +1646,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1665,7 +1668,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1676,7 +1679,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1687,7 +1690,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1714,7 +1717,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1851,7 +1854,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1862,7 +1865,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1873,7 +1876,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1884,7 +1887,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -1899,30 +1902,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="221">
   <si>
     <t>targa</t>
   </si>
@@ -569,112 +569,115 @@
     <t>SCACCIA FEDERICA</t>
   </si>
   <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>SOFIA.D'ANGELO</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>LELLA PATERNITA' - FERMA A LANCIANO</t>
   </si>
 </sst>
 </file>
@@ -1797,6 +1800,9 @@
       <c r="B88" t="s">
         <v>184</v>
       </c>
+      <c r="C88" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" t="s">
@@ -1854,7 +1860,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1865,7 +1871,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1876,7 +1882,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1902,30 +1908,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -401,283 +401,283 @@
     <t>MAGRI MARILENA</t>
   </si>
   <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>MARIALUCIA.DELRE</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN (TEMPORANEAMENTE PER TAGLIANDO)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>CELA REZEARTA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN (TEMPORANEAMENTE PER TAGLIANDO)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>SOFIA.D'ANGELO</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1295,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1394,7 +1394,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1461,7 +1461,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1472,7 +1472,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1507,7 +1507,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1550,7 +1550,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1649,7 +1649,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1671,7 +1671,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1682,7 +1682,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1693,7 +1693,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1720,7 +1720,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1801,7 +1801,7 @@
         <v>184</v>
       </c>
       <c r="C88" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1893,7 +1893,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -1922,16 +1922,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
         <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -437,247 +437,247 @@
     <t>LEPORATI PEREZ.MELANY LUNA</t>
   </si>
   <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CARAVAGGIO.MARISA</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>DE TOMMASO SONIA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>ALIAJ.KLODIAN (TEMPORANEAMENTE PER TAGLIANDO)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-05-25</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CELA REZEARTA</t>
   </si>
 </sst>
 </file>
@@ -1922,16 +1922,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
         <v>220</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -590,94 +590,97 @@
     <t>KALOV SLAVI KRASIMIROV</t>
   </si>
   <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DE TOMMASO SONIA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN (TEMPORANEAMENTE PER TAGLIANDO)</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1896,7 @@
         <v>191</v>
       </c>
       <c r="C98" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1908,30 +1911,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -410,277 +410,277 @@
     <t>FEDERICA.DIREMIGIO</t>
   </si>
   <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>CONSOL</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>MARIALUCIA.DELRE</t>
   </si>
   <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
     <t>CARAVAGGIO.MARISA</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DE TOMMASO SONIA</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1046,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1084,7 +1084,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1111,7 +1111,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1138,7 +1138,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1149,7 +1149,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1176,7 +1176,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1187,7 +1187,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1198,7 +1198,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1209,7 +1209,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1220,7 +1220,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1287,7 +1287,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1298,7 +1298,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1322,7 +1322,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>101</v>
+      </c>
+      <c r="C33" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1330,7 +1333,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1338,7 +1341,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1346,7 +1349,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1354,7 +1357,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1362,7 +1365,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1370,7 +1373,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1378,7 +1381,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1386,7 +1389,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1394,10 +1397,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1405,7 +1408,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1413,7 +1416,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1421,7 +1424,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1429,7 +1432,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1437,7 +1440,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1445,7 +1448,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1453,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1461,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1472,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1483,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1491,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1499,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1507,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1518,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1526,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1534,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1542,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1550,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1561,7 +1564,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1569,7 +1572,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1577,7 +1580,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1585,7 +1588,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1593,7 +1596,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1601,7 +1604,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1609,7 +1612,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1617,7 +1620,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1625,7 +1628,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1633,7 +1636,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1641,7 +1644,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1649,10 +1652,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1660,10 +1663,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1671,10 +1674,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1682,10 +1685,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1693,10 +1696,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1704,7 +1707,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1712,7 +1715,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1720,10 +1723,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1731,7 +1734,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1739,7 +1742,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1747,10 +1750,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1758,10 +1761,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1769,7 +1772,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1777,7 +1780,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1785,7 +1788,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1793,7 +1796,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1801,10 +1804,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C88" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1812,7 +1815,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1820,7 +1823,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>186</v>
+        <v>101</v>
+      </c>
+      <c r="C90" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1828,7 +1834,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1836,7 +1842,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1844,7 +1850,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1852,7 +1858,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1860,10 +1866,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1871,10 +1877,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1882,10 +1888,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1893,10 +1899,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1906,35 +1912,49 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" t="s">
         <v>217</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>218</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>219</v>
-      </c>
-      <c r="D1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s">
         <v>221</v>
       </c>
-      <c r="C2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" t="s">
-        <v>216</v>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="220">
   <si>
     <t>targa</t>
   </si>
@@ -587,7 +587,7 @@
     <t>VINCIGUERRA MANUELA</t>
   </si>
   <si>
-    <t>2026-03-27</t>
+    <t>2026-06-10</t>
   </si>
   <si>
     <t>2026-05-07</t>
@@ -675,12 +675,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>MARIALUCIA.DELRE</t>
-  </si>
-  <si>
-    <t>CARAVAGGIO.MARISA</t>
   </si>
 </sst>
 </file>
@@ -1912,7 +1906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1931,30 +1925,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="222">
   <si>
     <t>targa</t>
   </si>
@@ -503,178 +503,184 @@
     <t>PITOLI.PAULA RENATA</t>
   </si>
   <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PIRA ROMINA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>CONSOL</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1592,6 +1598,9 @@
       <c r="B65" t="s">
         <v>162</v>
       </c>
+      <c r="C65" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
@@ -1649,7 +1658,7 @@
         <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1671,7 +1680,7 @@
         <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1682,7 +1691,7 @@
         <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1693,7 +1702,7 @@
         <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1720,7 +1729,7 @@
         <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1863,7 +1872,7 @@
         <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1874,7 +1883,7 @@
         <v>145</v>
       </c>
       <c r="C96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1885,7 +1894,7 @@
         <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1896,7 +1905,7 @@
         <v>189</v>
       </c>
       <c r="C98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -1911,30 +1920,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -551,136 +551,136 @@
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>PIRA ROMINA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>CONSOL</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1046,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1084,7 +1084,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1111,7 +1111,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1138,7 +1138,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1149,7 +1149,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1176,7 +1176,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1187,7 +1187,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1198,7 +1198,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1209,7 +1209,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1220,7 +1220,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1287,7 +1287,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1298,7 +1298,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1325,7 +1325,7 @@
         <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1400,7 +1400,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1467,7 +1467,7 @@
         <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1478,7 +1478,7 @@
         <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1513,7 +1513,7 @@
         <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1556,7 +1556,7 @@
         <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1599,7 +1599,7 @@
         <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1658,7 +1658,7 @@
         <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1669,7 +1669,7 @@
         <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1680,7 +1680,7 @@
         <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1691,7 +1691,7 @@
         <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1702,7 +1702,7 @@
         <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1729,7 +1729,7 @@
         <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1756,7 +1756,7 @@
         <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1767,7 +1767,7 @@
         <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1807,10 +1807,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1837,7 +1837,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1845,7 +1845,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1853,7 +1853,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1861,7 +1861,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1902,7 +1902,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
         <v>216</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -365,322 +365,322 @@
     <t>MARCHIONDA ILARIA</t>
   </si>
   <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-01-28</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>PIRA ROMINA</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1046,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1084,7 +1084,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1111,7 +1111,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1138,7 +1138,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1149,7 +1149,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1176,7 +1176,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1184,10 +1184,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1195,10 +1195,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1206,10 +1206,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1217,10 +1217,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1228,7 +1228,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1236,7 +1236,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1244,7 +1244,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1252,7 +1252,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1260,7 +1260,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1268,7 +1268,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1276,7 +1276,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1284,10 +1284,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1295,10 +1295,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1306,7 +1306,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1314,7 +1314,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1325,7 +1325,7 @@
         <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1333,7 +1333,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1341,7 +1341,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1349,7 +1349,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1357,7 +1357,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1365,7 +1365,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1373,7 +1373,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1381,7 +1381,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1389,7 +1389,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1397,10 +1397,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1408,7 +1408,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1416,7 +1416,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1424,7 +1424,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1432,7 +1432,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1440,7 +1440,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1448,7 +1448,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1456,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1464,10 +1464,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1475,10 +1475,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1486,7 +1486,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1494,7 +1494,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1502,7 +1502,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1510,10 +1510,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1521,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1529,7 +1529,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1537,7 +1537,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1545,7 +1545,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1553,10 +1553,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1564,7 +1564,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1572,7 +1572,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1580,7 +1580,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1588,7 +1588,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1596,10 +1596,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1607,7 +1607,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1615,7 +1615,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1623,7 +1623,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1631,7 +1631,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1639,7 +1639,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1647,7 +1647,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1655,10 +1655,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1666,10 +1666,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1677,10 +1677,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1688,10 +1688,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1699,10 +1699,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1710,7 +1710,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1718,7 +1718,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1726,10 +1726,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1737,7 +1737,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1745,7 +1745,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1753,10 +1753,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1764,7 +1764,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
         <v>213</v>
@@ -1775,7 +1775,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1783,7 +1783,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1791,7 +1791,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1799,7 +1799,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1807,10 +1807,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1818,7 +1818,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1829,7 +1829,7 @@
         <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1837,7 +1837,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1845,7 +1845,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1853,7 +1853,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1861,7 +1861,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1869,7 +1869,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C95" t="s">
         <v>214</v>
@@ -1880,7 +1880,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96" t="s">
         <v>215</v>
@@ -1891,7 +1891,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C97" t="s">
         <v>214</v>
@@ -1902,7 +1902,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C98" t="s">
         <v>216</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="221">
   <si>
     <t>targa</t>
   </si>
@@ -365,6 +365,9 @@
     <t>MARCHIONDA ILARIA</t>
   </si>
   <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
     <t>MARSILI PAOLA</t>
   </si>
   <si>
@@ -536,7 +539,7 @@
     <t>SABINA.LANCIA</t>
   </si>
   <si>
-    <t>MASCIARELLI MAURIZIO</t>
+    <t>DA ASSEGNARE (LELLA)</t>
   </si>
   <si>
     <t>IEZZI.SERENA</t>
@@ -599,7 +602,7 @@
     <t>2026-05-18</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>2026-05-06</t>
@@ -650,9 +653,6 @@
     <t>2026-02-03</t>
   </si>
   <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
     <t>2026-04-30</t>
   </si>
   <si>
@@ -678,9 +678,6 @@
   </si>
   <si>
     <t>Data_Cambio</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (PROBLEMA AI FRENI)</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1043,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1084,7 +1081,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1111,7 +1108,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1138,7 +1135,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1149,7 +1146,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1176,7 +1173,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1184,10 +1181,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1195,10 +1192,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1206,10 +1203,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1217,10 +1214,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1228,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1236,7 +1233,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1244,7 +1241,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1252,7 +1249,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1260,7 +1257,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1268,7 +1265,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1276,7 +1273,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1284,10 +1281,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1295,10 +1292,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1306,7 +1303,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1314,7 +1311,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1325,7 +1322,7 @@
         <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1333,7 +1330,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1341,7 +1338,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1349,7 +1346,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1357,7 +1354,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1365,7 +1362,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1373,7 +1370,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1381,7 +1378,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1389,7 +1386,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1397,10 +1394,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1408,7 +1405,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1416,7 +1413,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1424,7 +1421,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1432,7 +1429,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1440,7 +1437,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1448,7 +1445,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1456,7 +1453,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1464,10 +1461,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1475,10 +1472,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1486,7 +1483,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1494,7 +1491,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1502,7 +1499,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1510,10 +1507,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1521,7 +1518,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1529,7 +1526,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1537,7 +1534,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1545,7 +1542,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1553,10 +1550,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1564,7 +1561,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1572,7 +1569,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1580,7 +1577,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1588,7 +1585,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1596,10 +1593,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1607,7 +1604,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1615,7 +1612,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1623,7 +1620,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1631,7 +1628,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1639,7 +1636,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1647,7 +1644,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1655,10 +1652,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1666,10 +1663,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1677,10 +1674,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1688,10 +1685,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1699,10 +1696,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1710,7 +1707,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1718,7 +1715,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1726,10 +1723,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1737,7 +1734,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1745,7 +1742,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1753,7 +1750,7 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
         <v>212</v>
@@ -1764,7 +1761,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
         <v>213</v>
@@ -1775,7 +1772,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1783,7 +1780,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1791,7 +1788,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1799,7 +1796,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1807,10 +1804,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1818,7 +1815,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1829,7 +1826,7 @@
         <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1837,7 +1834,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1845,7 +1842,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1853,7 +1850,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1861,7 +1858,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1869,7 +1866,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
         <v>214</v>
@@ -1880,7 +1877,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
         <v>215</v>
@@ -1891,7 +1888,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
         <v>214</v>
@@ -1902,7 +1899,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
         <v>216</v>
@@ -1915,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1934,16 +1931,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>101</v>
       </c>
-      <c r="D2" t="s">
-        <v>194</v>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="223">
   <si>
     <t>targa</t>
   </si>
@@ -410,6 +410,9 @@
     <t>FEDERICA.DIREMIGIO</t>
   </si>
   <si>
+    <t>CIMINO NORA (LA SUA FERMA DA PASQUARELLI )</t>
+  </si>
+  <si>
     <t>NATHALIE.BOVE</t>
   </si>
   <si>
@@ -620,43 +623,46 @@
     <t>2026-06-01</t>
   </si>
   <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
     <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
   </si>
   <si>
     <t>2025-12-18</t>
@@ -1043,7 +1049,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1081,7 +1087,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1108,7 +1114,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1135,7 +1141,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1146,7 +1152,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1173,7 +1179,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1184,7 +1190,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1195,7 +1201,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1206,7 +1212,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1217,7 +1223,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1284,7 +1290,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1295,7 +1301,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1319,10 +1325,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1330,7 +1336,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1338,7 +1344,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1346,7 +1352,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1354,7 +1360,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1362,7 +1368,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1370,7 +1376,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1378,7 +1384,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1386,7 +1392,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1394,10 +1400,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1405,7 +1411,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1413,7 +1419,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1421,7 +1427,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1429,7 +1435,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1437,7 +1443,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1445,7 +1451,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1453,7 +1459,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1461,10 +1467,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1472,10 +1478,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1483,7 +1489,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1491,7 +1497,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1499,7 +1505,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1507,10 +1513,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1518,7 +1524,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1526,7 +1532,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1534,7 +1540,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1542,7 +1548,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1550,10 +1556,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1561,7 +1567,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1569,7 +1575,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1577,7 +1583,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1585,7 +1591,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1593,10 +1599,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C65" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1604,7 +1610,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1612,7 +1618,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1620,7 +1626,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1628,7 +1634,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1636,7 +1642,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1644,7 +1650,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1652,10 +1658,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1663,10 +1669,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1674,10 +1680,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1685,10 +1691,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1696,10 +1702,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1707,7 +1713,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1715,7 +1721,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1723,10 +1729,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1734,7 +1740,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1742,7 +1748,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1750,10 +1756,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1761,10 +1767,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1772,7 +1778,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1780,7 +1786,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1788,7 +1794,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1796,7 +1802,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1804,10 +1810,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C88" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1815,7 +1821,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1826,7 +1832,7 @@
         <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1834,7 +1840,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1842,7 +1848,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1850,7 +1856,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1858,7 +1864,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1866,10 +1872,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1877,10 +1883,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1888,10 +1894,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1899,10 +1905,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1912,49 +1918,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D3" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="224">
   <si>
     <t>targa</t>
   </si>
@@ -554,21 +554,24 @@
     <t>BONFITTO DAVIDE</t>
   </si>
   <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
     <t>MENNUCCI MORENA</t>
   </si>
   <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
     <t>COCO.FEDERICO</t>
   </si>
   <si>
@@ -659,7 +662,7 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>2026-06-12</t>
+    <t>2026-06-29</t>
   </si>
   <si>
     <t>2026-06-08</t>
@@ -1049,7 +1052,7 @@
         <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1087,7 +1090,7 @@
         <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1114,7 +1117,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1141,7 +1144,7 @@
         <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1152,7 +1155,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1179,7 +1182,7 @@
         <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1190,7 +1193,7 @@
         <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1201,7 +1204,7 @@
         <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1212,7 +1215,7 @@
         <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1223,7 +1226,7 @@
         <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1290,7 +1293,7 @@
         <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1301,7 +1304,7 @@
         <v>128</v>
       </c>
       <c r="C30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1328,7 +1331,7 @@
         <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1403,7 +1406,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1470,7 +1473,7 @@
         <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1481,7 +1484,7 @@
         <v>149</v>
       </c>
       <c r="C51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1516,7 +1519,7 @@
         <v>153</v>
       </c>
       <c r="C55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1559,7 +1562,7 @@
         <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1602,7 +1605,7 @@
         <v>163</v>
       </c>
       <c r="C65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1661,7 +1664,7 @@
         <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1672,7 +1675,7 @@
         <v>146</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -1683,7 +1686,7 @@
         <v>146</v>
       </c>
       <c r="C74" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -1694,7 +1697,7 @@
         <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -1705,7 +1708,7 @@
         <v>172</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -1732,7 +1735,7 @@
         <v>175</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -1759,7 +1762,7 @@
         <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -1770,7 +1773,7 @@
         <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -1810,10 +1813,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -1821,7 +1824,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1832,7 +1835,7 @@
         <v>101</v>
       </c>
       <c r="C90" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -1840,7 +1843,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1848,7 +1851,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1856,7 +1859,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1864,7 +1867,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1875,7 +1878,7 @@
         <v>146</v>
       </c>
       <c r="C95" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -1886,7 +1889,7 @@
         <v>146</v>
       </c>
       <c r="C96" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -1897,7 +1900,7 @@
         <v>146</v>
       </c>
       <c r="C97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -1905,10 +1908,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C98" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -1923,30 +1926,30 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/flotta.xlsx
+++ b/flotta.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="225">
   <si>
     <t>targa</t>
   </si>
@@ -317,376 +317,379 @@
     <t>GL352TJ</t>
   </si>
   <si>
+    <t>DA ASSEGNARE</t>
+  </si>
+  <si>
+    <t>STEFANO.CAMPLONE</t>
+  </si>
+  <si>
+    <t>ALIAJ.KLODIAN</t>
+  </si>
+  <si>
+    <t>TELEASA GEANINA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (INCIDENTATA)</t>
+  </si>
+  <si>
+    <t>MONICA.LENKA</t>
+  </si>
+  <si>
+    <t>VALERY.PACELLA</t>
+  </si>
+  <si>
+    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
+  </si>
+  <si>
+    <t>SIMONA.PETRAGNANO</t>
+  </si>
+  <si>
+    <t>ALESSIA.DE LUCA</t>
+  </si>
+  <si>
+    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
+  </si>
+  <si>
+    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
+  </si>
+  <si>
+    <t>CINZIA.D'ORAZIO</t>
+  </si>
+  <si>
+    <t>DI TIZIO.VALENTINA</t>
+  </si>
+  <si>
+    <t>MARCHIONDA ILARIA</t>
+  </si>
+  <si>
+    <t>MASCIARELLI MAURIZIO</t>
+  </si>
+  <si>
+    <t>MARSILI PAOLA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
+  </si>
+  <si>
+    <t>JANE LUCIANO</t>
+  </si>
+  <si>
+    <t>MARATEA.FELICIA</t>
+  </si>
+  <si>
+    <t>ANTONIO.BRUNO</t>
+  </si>
+  <si>
+    <t>MARIA.LUCIANO</t>
+  </si>
+  <si>
+    <t>MIMOZA.TREPSENISHTI</t>
+  </si>
+  <si>
+    <t>ELEONORA:PERINO</t>
+  </si>
+  <si>
+    <t>LORENZA.COLABRUNO</t>
+  </si>
+  <si>
+    <t>MICAELA.POSTIGLIONE</t>
+  </si>
+  <si>
+    <t>MAGRI MARILENA</t>
+  </si>
+  <si>
+    <t>CINOSI MELANIA</t>
+  </si>
+  <si>
+    <t>MICHELA.VOCIONE</t>
+  </si>
+  <si>
+    <t>FEDERICA.DIREMIGIO</t>
+  </si>
+  <si>
+    <t>CIMINO NORA (LA SUA FERMA DA PASQUARELLI )</t>
+  </si>
+  <si>
+    <t>NATHALIE.BOVE</t>
+  </si>
+  <si>
+    <t>SECRIERU.NATALIA</t>
+  </si>
+  <si>
+    <t>FELICIA.FALCONIO</t>
+  </si>
+  <si>
+    <t>AURORA.TARANTINI</t>
+  </si>
+  <si>
+    <t>PIERPAOLO.ALEMANNO</t>
+  </si>
+  <si>
+    <t>ESTER.FECONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR.FINIZII </t>
+  </si>
+  <si>
+    <t>LEPORATI PEREZ.MELANY LUNA</t>
+  </si>
+  <si>
+    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>DIEGO.PANTALONE</t>
+  </si>
+  <si>
+    <t>MARCELLA.TRIVARELLI</t>
+  </si>
+  <si>
+    <t>GIADA.GIANSALVO</t>
+  </si>
+  <si>
+    <t>GIULIA.RENZETTI</t>
+  </si>
+  <si>
+    <t>LORELLAD'ORTONA</t>
+  </si>
+  <si>
+    <t>FINE RENT</t>
+  </si>
+  <si>
+    <t>SIMONA.TURDò</t>
+  </si>
+  <si>
+    <t>PAINAT CRISTINA</t>
+  </si>
+  <si>
+    <t>CANDELORO AUGUSTA</t>
+  </si>
+  <si>
+    <t>MATTEO.CERRITETLLI</t>
+  </si>
+  <si>
+    <t>MILENA.IANNIELLO</t>
+  </si>
+  <si>
+    <t>DOINA.ATANASOAEI</t>
+  </si>
+  <si>
+    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>FRANCESCO.DI.DOMENICANTONIO</t>
+  </si>
+  <si>
+    <t>NORA.CIMINO</t>
+  </si>
+  <si>
+    <t>GIANLUCA.LUCIANI</t>
+  </si>
+  <si>
+    <t>ALESSIO.PELLICCIA</t>
+  </si>
+  <si>
+    <t>NARDECCHIA CHIARA</t>
+  </si>
+  <si>
+    <t>GIUSEPPE.GRAVINA</t>
+  </si>
+  <si>
+    <t>BEATRICE.D'INNOCENZO</t>
+  </si>
+  <si>
+    <t>FRANCESCA.COTOLESSA</t>
+  </si>
+  <si>
+    <t>PITOLI.PAULA RENATA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (MULETTO)</t>
+  </si>
+  <si>
+    <t>ANTONINO.MICOZZI</t>
+  </si>
+  <si>
+    <t>PAOLA.VADANESCU</t>
+  </si>
+  <si>
+    <t>MOANA.DIFRANCESCO</t>
+  </si>
+  <si>
+    <t>SALVATORE.ALEMANNI</t>
+  </si>
+  <si>
+    <t>MARICA.SPADACCINI</t>
+  </si>
+  <si>
+    <t>TONIA DE TOMMASO</t>
+  </si>
+  <si>
+    <t>BENEGIAMO VALERIA</t>
+  </si>
+  <si>
+    <t>ELIANA PARDI</t>
+  </si>
+  <si>
+    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
+  </si>
+  <si>
+    <t>LAURA.STANISCI</t>
+  </si>
+  <si>
+    <t>SABINA.LANCIA</t>
+  </si>
+  <si>
+    <t>DA ASSEGNARE (LELLA)</t>
+  </si>
+  <si>
+    <t>IEZZI.SERENA</t>
+  </si>
+  <si>
+    <t>MARCO.DI.NIZO</t>
+  </si>
+  <si>
+    <t>BONFITTO DAVIDE</t>
+  </si>
+  <si>
+    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
+  </si>
+  <si>
+    <t>VALERIO.D'ANTONIO</t>
+  </si>
+  <si>
+    <t>YOEL.DESPAIGNE</t>
+  </si>
+  <si>
+    <t>ERIKA.PATELLA</t>
+  </si>
+  <si>
+    <t>SCACCIA FEDERICA</t>
+  </si>
+  <si>
+    <t>MENNUCCI MORENA</t>
+  </si>
+  <si>
+    <t>COCO.FEDERICO</t>
+  </si>
+  <si>
+    <t>CHIARA.MANCINI</t>
+  </si>
+  <si>
+    <t>MATTEO.CAVACINI</t>
+  </si>
+  <si>
+    <t>COMPARELLI</t>
+  </si>
+  <si>
+    <t>KALOV SLAVI KRASIMIROV</t>
+  </si>
+  <si>
+    <t>VINCIGUERRA MANUELA</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>2026-01-09</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2025-12-18</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>Operatore_Precedente</t>
+  </si>
+  <si>
+    <t>Nuovo_Operatore</t>
+  </si>
+  <si>
+    <t>Data_Cambio</t>
+  </si>
+  <si>
     <t>RUSSO.ZAIRA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE</t>
-  </si>
-  <si>
-    <t>STEFANO.CAMPLONE</t>
-  </si>
-  <si>
-    <t>ALIAJ.KLODIAN</t>
-  </si>
-  <si>
-    <t>TELEASA GEANINA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (INCIDENTATA)</t>
-  </si>
-  <si>
-    <t>MONICA.LENKA</t>
-  </si>
-  <si>
-    <t>VALERY.PACELLA</t>
-  </si>
-  <si>
-    <t>VALERY PACELLA (SENTIRE TEODORA)</t>
-  </si>
-  <si>
-    <t>SIMONA.PETRAGNANO</t>
-  </si>
-  <si>
-    <t>ALESSIA.DE LUCA</t>
-  </si>
-  <si>
-    <t>INCEDENTATA  - NON ASSEGNARE - CENTRO DAMA</t>
-  </si>
-  <si>
-    <t>MICHELA VOCIONE (ASS. TEMPORANEA UN MESE)</t>
-  </si>
-  <si>
-    <t>CINZIA.D'ORAZIO</t>
-  </si>
-  <si>
-    <t>DI TIZIO.VALENTINA</t>
-  </si>
-  <si>
-    <t>MARCHIONDA ILARIA</t>
-  </si>
-  <si>
-    <t>MASCIARELLI MAURIZIO</t>
-  </si>
-  <si>
-    <t>MARSILI PAOLA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE° (PRIMA DA PORTARE DA PASQUARELLI PER PROBLEMA AI FRENI)</t>
-  </si>
-  <si>
-    <t>JANE LUCIANO</t>
-  </si>
-  <si>
-    <t>MARATEA.FELICIA</t>
-  </si>
-  <si>
-    <t>ANTONIO.BRUNO</t>
-  </si>
-  <si>
-    <t>MARIA.LUCIANO</t>
-  </si>
-  <si>
-    <t>MIMOZA.TREPSENISHTI</t>
-  </si>
-  <si>
-    <t>ELEONORA:PERINO</t>
-  </si>
-  <si>
-    <t>LORENZA.COLABRUNO</t>
-  </si>
-  <si>
-    <t>MICAELA.POSTIGLIONE</t>
-  </si>
-  <si>
-    <t>MAGRI MARILENA</t>
-  </si>
-  <si>
-    <t>CINOSI MELANIA</t>
-  </si>
-  <si>
-    <t>MICHELA.VOCIONE</t>
-  </si>
-  <si>
-    <t>FEDERICA.DIREMIGIO</t>
-  </si>
-  <si>
-    <t>CIMINO NORA (LA SUA FERMA DA PASQUARELLI )</t>
-  </si>
-  <si>
-    <t>NATHALIE.BOVE</t>
-  </si>
-  <si>
-    <t>SECRIERU.NATALIA</t>
-  </si>
-  <si>
-    <t>FELICIA.FALCONIO</t>
-  </si>
-  <si>
-    <t>AURORA.TARANTINI</t>
-  </si>
-  <si>
-    <t>PIERPAOLO.ALEMANNO</t>
-  </si>
-  <si>
-    <t>ESTER.FECONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NADIR.FINIZII </t>
-  </si>
-  <si>
-    <t>LEPORATI PEREZ.MELANY LUNA</t>
-  </si>
-  <si>
-    <t>ZACCAGNINO ROCCO (LA SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>DIEGO.PANTALONE</t>
-  </si>
-  <si>
-    <t>MARCELLA.TRIVARELLI</t>
-  </si>
-  <si>
-    <t>GIADA.GIANSALVO</t>
-  </si>
-  <si>
-    <t>GIULIA.RENZETTI</t>
-  </si>
-  <si>
-    <t>LORELLAD'ORTONA</t>
-  </si>
-  <si>
-    <t>FINE RENT</t>
-  </si>
-  <si>
-    <t>SIMONA.TURDò</t>
-  </si>
-  <si>
-    <t>PAINAT CRISTINA</t>
-  </si>
-  <si>
-    <t>CANDELORO AUGUSTA</t>
-  </si>
-  <si>
-    <t>MATTEO.CERRITETLLI</t>
-  </si>
-  <si>
-    <t>MILENA.IANNIELLO</t>
-  </si>
-  <si>
-    <t>DOINA.ATANASOAEI</t>
-  </si>
-  <si>
-    <t>LEPORATI  PEREZE MELANY LUNA (LA SUA AUTO GL 347TJ-IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>FRANCESCO.DI.DOMENICANTONIO</t>
-  </si>
-  <si>
-    <t>NORA.CIMINO</t>
-  </si>
-  <si>
-    <t>GIANLUCA.LUCIANI</t>
-  </si>
-  <si>
-    <t>ALESSIO.PELLICCIA</t>
-  </si>
-  <si>
-    <t>NARDECCHIA CHIARA</t>
-  </si>
-  <si>
-    <t>GIUSEPPE.GRAVINA</t>
-  </si>
-  <si>
-    <t>BEATRICE.D'INNOCENZO</t>
-  </si>
-  <si>
-    <t>FRANCESCA.COTOLESSA</t>
-  </si>
-  <si>
-    <t>PITOLI.PAULA RENATA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (MULETTO)</t>
-  </si>
-  <si>
-    <t>ANTONINO.MICOZZI</t>
-  </si>
-  <si>
-    <t>PAOLA.VADANESCU</t>
-  </si>
-  <si>
-    <t>MOANA.DIFRANCESCO</t>
-  </si>
-  <si>
-    <t>SALVATORE.ALEMANNI</t>
-  </si>
-  <si>
-    <t>MARICA.SPADACCINI</t>
-  </si>
-  <si>
-    <t>TONIA DE TOMMASO</t>
-  </si>
-  <si>
-    <t>BENEGIAMO VALERIA</t>
-  </si>
-  <si>
-    <t>ELIANA PARDI</t>
-  </si>
-  <si>
-    <t>ROCCO ZACCAGNIGNO (MOMENTANEO, SUA IN ASSISTENZA)</t>
-  </si>
-  <si>
-    <t>LAURA.STANISCI</t>
-  </si>
-  <si>
-    <t>SABINA.LANCIA</t>
-  </si>
-  <si>
-    <t>DA ASSEGNARE (LELLA)</t>
-  </si>
-  <si>
-    <t>IEZZI.SERENA</t>
-  </si>
-  <si>
-    <t>MARCO.DI.NIZO</t>
-  </si>
-  <si>
-    <t>BONFITTO DAVIDE</t>
-  </si>
-  <si>
-    <t>PESCE STEFANO (FISIOTERAPISTA) - MASSIMO 30 GG</t>
-  </si>
-  <si>
-    <t>VALERIO.D'ANTONIO</t>
-  </si>
-  <si>
-    <t>YOEL.DESPAIGNE</t>
-  </si>
-  <si>
-    <t>ERIKA.PATELLA</t>
-  </si>
-  <si>
-    <t>SCACCIA FEDERICA</t>
-  </si>
-  <si>
-    <t>MENNUCCI MORENA</t>
-  </si>
-  <si>
-    <t>COCO.FEDERICO</t>
-  </si>
-  <si>
-    <t>CHIARA.MANCINI</t>
-  </si>
-  <si>
-    <t>MATTEO.CAVACINI</t>
-  </si>
-  <si>
-    <t>COMPARELLI</t>
-  </si>
-  <si>
-    <t>KALOV SLAVI KRASIMIROV</t>
-  </si>
-  <si>
-    <t>VINCIGUERRA MANUELA</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-04-16</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>2026-04-23</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-04-29</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>Operatore_Precedente</t>
-  </si>
-  <si>
-    <t>Nuovo_Operatore</t>
-  </si>
-  <si>
-    <t>Data_Cambio</t>
   </si>
 </sst>
 </file>
@@ -1043,13 +1046,16 @@
       <c r="B2" t="s">
         <v>100</v>
       </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
         <v>191</v>
@@ -1060,7 +1066,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1068,7 +1074,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1076,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="1">
         <v>45851</v>
@@ -1087,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
         <v>192</v>
@@ -1098,7 +1104,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1106,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1114,7 +1120,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
         <v>193</v>
@@ -1125,7 +1131,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1133,7 +1139,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1141,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
         <v>194</v>
@@ -1152,7 +1158,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
         <v>195</v>
@@ -1163,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1171,7 +1177,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1179,7 +1185,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
         <v>196</v>
@@ -1190,7 +1196,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
         <v>197</v>
@@ -1201,7 +1207,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
         <v>198</v>
@@ -1212,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
         <v>199</v>
@@ -1223,7 +1229,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
         <v>200</v>
@@ -1234,7 +1240,7 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1242,7 +1248,7 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1250,7 +1256,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1258,7 +1264,7 @@
         <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1266,7 +1272,7 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1274,7 +1280,7 @@
         <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1282,7 +1288,7 @@
         <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1290,7 +1296,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C29" t="s">
         <v>201</v>
@@ -1301,7 +1307,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C30" t="s">
         <v>202</v>
@@ -1312,7 +1318,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1320,7 +1326,7 @@
         <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1328,7 +1334,7 @@
         <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C33" t="s">
         <v>203</v>
@@ -1339,7 +1345,7 @@
         <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1347,7 +1353,7 @@
         <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1355,7 +1361,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1363,7 +1369,7 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1371,7 +1377,7 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1379,7 +1385,7 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1387,7 +1393,7 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1395,7 +1401,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1403,7 +1409,7 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
         <v>204</v>
@@ -1414,7 +1420,7 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1422,7 +1428,7 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1430,7 +1436,7 @@
         <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1438,7 +1444,7 @@
         <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1446,7 +1452,7 @@
         <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1454,7 +1460,7 @@
         <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1462,7 +1468,7 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1470,7 +1476,7 @@
         <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
         <v>205</v>
@@ -1481,7 +1487,7 @@
         <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C51" t="s">
         <v>206</v>
@@ -1492,7 +1498,7 @@
         <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1500,7 +1506,7 @@
         <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1508,7 +1514,7 @@
         <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1516,7 +1522,7 @@
         <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
         <v>207</v>
@@ -1527,7 +1533,7 @@
         <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1535,7 +1541,7 @@
         <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1543,7 +1549,7 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1551,7 +1557,7 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1559,7 +1565,7 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
         <v>208</v>
@@ -1570,7 +1576,7 @@
         <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1578,7 +1584,7 @@
         <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1586,7 +1592,7 @@
         <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1594,7 +1600,7 @@
         <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1602,7 +1608,7 @@
         <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C65" t="s">
         <v>209</v>
@@ -1613,7 +1619,7 @@
         <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1621,7 +1627,7 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1629,7 +1635,7 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1637,7 +1643,7 @@
         <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1645,7 +1651,7 @@
         <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1653,7 +1659,7 @@
         <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1661,7 +1667,7 @@
         <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C72" t="s">
         <v>210</v>
@@ -1672,7 +1678,7 @@
         <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
         <v>195</v>
@@ -1683,7 +1689,7 @@
         <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
         <v>211</v>
@@ -1694,7 +1700,7 @@
         <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
         <v>212</v>
@@ -1705,7 +1711,7 @@
         <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
         <v>213</v>
@@ -1716,7 +1722,7 @@
         <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -1724,7 +1730,7 @@
         <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -1732,7 +1738,7 @@
         <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
         <v>197</v>
@@ -1743,7 +1749,7 @@
         <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -1751,7 +1757,7 @@
         <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -1759,7 +1765,7 @@
         <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
         <v>214</v>
@@ -1770,7 +1776,7 @@
         <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
         <v>215</v>
@@ -1781,7 +1787,7 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -1789,7 +1795,7 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -1797,7 +1803,7 @@
         <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -1805,7 +1811,7 @@
         <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -1813,7 +1819,7 @@
         <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C88" t="s">
         <v>202</v>
@@ -1824,7 +1830,7 @@
         <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -1832,7 +1838,7 @@
         <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C90" t="s">
         <v>216</v>
@@ -1843,7 +1849,7 @@
         <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -1851,7 +1857,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -1859,7 +1865,7 @@
         <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -1867,7 +1873,7 @@
         <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -1875,7 +1881,7 @@
         <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
         <v>217</v>
@@ -1886,7 +1892,7 @@
         <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" t="s">
         <v>218</v>
@@ -1897,7 +1903,7 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
         <v>217</v>
@@ -1908,7 +1914,7 @@
         <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C98" t="s">
         <v>219</v>
@@ -1940,16 +1946,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
